--- a/human_validation/judge/en/judge_D003_S001_P001__qwen3-235b.xlsx
+++ b/human_validation/judge/en/judge_D003_S001_P001__qwen3-235b.xlsx
@@ -461,6 +461,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -558,6 +559,7 @@
         <v>0</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
